--- a/inst/extdata/region/2026-08-11/wb_projects_gov_eca.xlsx
+++ b/inst/extdata/region/2026-08-11/wb_projects_gov_eca.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -121,15 +121,6 @@
   </si>
   <si>
     <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">P172924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional Financing for Public Finance Management Modernization Project 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P172924</t>
   </si>
   <si>
     <t xml:space="preserve">P171892</t>
@@ -720,7 +711,7 @@
         <v>37</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>25</v>
@@ -737,34 +728,34 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>29</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>6000000</v>
+        <v>50000000</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" s="2" t="n">
         <v>0</v>
@@ -778,22 +769,22 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>2021</v>
@@ -801,25 +792,25 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>50000000</v>
+        <v>60000000</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>1</v>
@@ -828,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" s="2" t="n">
         <v>0</v>
@@ -837,70 +828,6 @@
         <v>34</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="V5" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1009,22 +936,22 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>2026</v>
@@ -1033,20 +960,20 @@
         <v>46196</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -1063,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="V2" s="2" t="s">
         <v>35</v>
@@ -1071,13 +998,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>25</v>
@@ -1095,20 +1022,20 @@
         <v>46072</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2" t="s">
         <v>31</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
@@ -1125,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="V3" s="2" t="s">
         <v>35</v>
